--- a/artfynd/A 40701-2023 artfynd.xlsx
+++ b/artfynd/A 40701-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40701-2023 artfynd.xlsx
+++ b/artfynd/A 40701-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>591136</v>
+        <v>86370680</v>
       </c>
       <c r="B2" t="n">
-        <v>93144</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2667</v>
+        <v>226</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Skuggorangelav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Caloplaca lucifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stensnäs N E-22, Bl</t>
+          <t>300 m N om Stensnäs, Bl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481682.5147592468</v>
+        <v>481751</v>
       </c>
       <c r="R2" t="n">
-        <v>6225609.779212812</v>
+        <v>6225338</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2005-10-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1989-05-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2005-10-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens inventering av skyddsvärda träd. Noterad av Ivar Björegren.</t>
+          <t>1989-05-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,21 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>ek</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Annika Lydänge</t>
+          <t>Stefan Ekman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Annika Lydänge</t>
+          <t>Ulf Arup, Stefan Ekman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Åtgärdsprogram för hotade arter</t>
+          <t>Skyddsvärda lavar i sydvästra Sverige</t>
         </is>
       </c>
     </row>
@@ -799,12 +784,7 @@
         <v>173593</v>
       </c>
       <c r="B3" t="n">
-        <v>88269</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481723.6615759854</v>
+        <v>481724</v>
       </c>
       <c r="R3" t="n">
-        <v>6225319.064769053</v>
+        <v>6225319</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,19 +849,9 @@
           <t>2005-10-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2005-10-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -917,57 +887,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>83598349</v>
+        <v>86370677</v>
       </c>
       <c r="B4" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>1114</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gammelekslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lecanographa amylacea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ask (Skyddsvärt träd), Bl</t>
+          <t>300 m N om Stensnäs, Bl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481682.5147592468</v>
+        <v>481751</v>
       </c>
       <c r="R4" t="n">
-        <v>6225609.779212812</v>
+        <v>6225338</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,29 +950,19 @@
           <t>Mörrum</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>E7C640F9-35B5-41F6-BDC9-E2392751B31E</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2005-10-26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1989-05-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2005-10-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1989-05-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>mycket sparsamt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,19 +973,346 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>ek</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Stefan Ekman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ulf Arup, Stefan Ekman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Skyddsvärda lavar i sydvästra Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>86370678</v>
+      </c>
+      <c r="B5" t="n">
+        <v>75390</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grå skärelav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dendrographa decolorans</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>300 m N om Stensnäs, Bl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>481751</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6225338</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlshamn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Mörrum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1989-05-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1989-05-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>ek</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Stefan Ekman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulf Arup, Stefan Ekman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Skyddsvärda lavar i sydvästra Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>591136</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96437</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stensnäs N E-22, Bl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>481683</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6225610</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Karlshamn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Mörrum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2005-10-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2005-10-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens inventering av skyddsvärda träd. Noterad av Ivar Björegren.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Annika Lydänge</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Annika Lydänge</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>83598349</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ask (Skyddsvärt träd), Bl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>481683</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6225610</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Karlshamn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Mörrum</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>E7C640F9-35B5-41F6-BDC9-E2392751B31E</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2005-10-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2005-10-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Johan Karlsson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Johan Karlsson, Ivar Björegren</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Trädportalen</t>
         </is>

--- a/artfynd/A 40701-2023 artfynd.xlsx
+++ b/artfynd/A 40701-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Skyddsvärda lavar i sydvästra Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86370680</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/173593</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
           <t>Skyddsvärda lavar i sydvästra Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86370677</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
           <t>Skyddsvärda lavar i sydvästra Sverige</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86370678</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/591136</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1317,8 +1347,21 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83598349</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>